--- a/docs/data/contributors.xlsx
+++ b/docs/data/contributors.xlsx
@@ -751,7 +751,7 @@
     <t xml:space="preserve">maize</t>
   </si>
   <si>
-    <t xml:space="preserve">Meaning of words hajwan and dʒanawar</t>
+    <t xml:space="preserve">Meaning of words hajwan and janawar</t>
   </si>
   <si>
     <t xml:space="preserve">Dasha Tsikh</t>
@@ -852,7 +852,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -886,10 +886,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4614,7 +4610,7 @@
       <c r="B75" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="8" t="s">
         <v>243</v>
       </c>
       <c r="D75" s="2" t="s">
